--- a/branches/main/ValueSet-mii-vs-icu-code-monitoring-und-vitaldaten-iso11073.xlsx
+++ b/branches/main/ValueSet-mii-vs-icu-code-monitoring-und-vitaldaten-iso11073.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="126">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2027.0.0-ballot.3</t>
+    <t>2027.0.0-ballot.3-rc.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -105,268 +105,283 @@
     <t>150017</t>
   </si>
   <si>
-    <t>Systolic blood pressure</t>
+    <t>MDC_PRESS_BLD_SYS</t>
   </si>
   <si>
     <t>150019</t>
   </si>
   <si>
-    <t>Mean blood pressure</t>
+    <t>MDC_PRESS_BLD_MEAN</t>
   </si>
   <si>
     <t>150018</t>
   </si>
   <si>
-    <t>Diastolic blood pressure</t>
+    <t>MDC_PRESS_BLD_DIA</t>
   </si>
   <si>
     <t>150084</t>
   </si>
   <si>
-    <t>Central venous pressure</t>
+    <t>MDC_PRESS_BLD_VEN_CENT</t>
   </si>
   <si>
     <t>150045</t>
   </si>
   <si>
-    <t>Systolic pulmonary arterial pressure</t>
+    <t>MDC_PRESS_BLD_ART_PULM_SYS</t>
   </si>
   <si>
     <t>150047</t>
   </si>
   <si>
-    <t>Mean pulmonary arterial pressure</t>
+    <t>MDC_PRESS_BLD_ART_PULM_MEAN</t>
   </si>
   <si>
     <t>150046</t>
   </si>
   <si>
-    <t>Diastolic pulmonary arterial pressure</t>
+    <t>MDC_PRESS_BLD_ART_PULM_DIA</t>
   </si>
   <si>
     <t>150052</t>
   </si>
   <si>
-    <t>Pulmonary artery wedge pressure</t>
+    <t>MDC_PRESS_BLD_ART_PULM_OCCL</t>
   </si>
   <si>
     <t>150276</t>
   </si>
   <si>
-    <t>Cardiac output</t>
+    <t>MDC_OUTPUT_CARD</t>
   </si>
   <si>
     <t>149772</t>
   </si>
   <si>
-    <t>Cardiac index</t>
+    <t>MDC_OUTPUT_CARD_INDEX</t>
   </si>
   <si>
     <t>149760</t>
   </si>
   <si>
-    <t>Systemic vascular resistance indexed</t>
+    <t>MDC_RES_VASC_SYS_INDEX</t>
   </si>
   <si>
     <t>152852</t>
   </si>
   <si>
-    <t>Pulmonary Vascular Resistance Index</t>
+    <t>MDC_RES_VASC_PULM_INDEX</t>
   </si>
   <si>
     <t>150428</t>
   </si>
   <si>
-    <t>Ventricular stroke</t>
+    <t>MDC_WK_LV_STROKE</t>
   </si>
   <si>
     <t>149764</t>
   </si>
   <si>
-    <t>Left Ventricular Stroke Work Index</t>
+    <t>MDC_WK_LV_STROKE_INDEX</t>
   </si>
   <si>
     <t>150368</t>
   </si>
   <si>
-    <t>Body temperature - Core</t>
+    <t>MDC_TEMP_CORE</t>
   </si>
   <si>
     <t>150456</t>
   </si>
   <si>
-    <t>Oxygen saturation in Arterial blood by Pulse oximetry</t>
+    <t>MDC_PULS_OXIM_SAT_O2</t>
   </si>
   <si>
     <t>160300</t>
   </si>
   <si>
-    <t>Postductal SpO2</t>
+    <t>MDC_PULS_OXIM_SAT_O2_ART_POSTDUCTAL</t>
   </si>
   <si>
     <t>160296</t>
   </si>
   <si>
-    <t>Preductal SpO2</t>
+    <t>MDC_PULS_OXIM_SAT_O2_ART_PREDUCTAL</t>
   </si>
   <si>
     <t>153608</t>
   </si>
   <si>
-    <t>Intracranial pressure</t>
+    <t>MDC_PRESS_INTRA_CRAN</t>
   </si>
   <si>
     <t>150103</t>
   </si>
   <si>
-    <t>Mean left ventricular pressure</t>
+    <t>MDC_PRESS_BLD_VENT_LEFT_MEAN</t>
   </si>
   <si>
     <t>150107</t>
   </si>
   <si>
-    <t>Mean right ventricular pressure</t>
+    <t>MDC_PRESS_BLD_VENT_RIGHT_MEAN</t>
   </si>
   <si>
     <t>150101</t>
   </si>
   <si>
-    <t>Systolic left ventricular pressure</t>
+    <t>MDC_PRESS_BLD_VENT_LEFT_SYS</t>
   </si>
   <si>
     <t>150105</t>
   </si>
   <si>
-    <t>Systolic right ventricular pressure</t>
+    <t>MDC_PRESS_BLD_VENT_RIGHT_SYS</t>
   </si>
   <si>
     <t>150102</t>
   </si>
   <si>
-    <t>Diastolic left ventricular pressure</t>
+    <t>MDC_PRESS_BLD_VENT_LEFT_DIA</t>
   </si>
   <si>
     <t>150106</t>
   </si>
   <si>
-    <t>Diastolic right ventricular pressure</t>
+    <t>MDC_PRESS_BLD_VENT_RIGHT_DIA</t>
   </si>
   <si>
     <t>150069</t>
   </si>
   <si>
-    <t>Systolic right atrial pressure</t>
+    <t>MDC_PRESS_BLD_ATR_RIGHT_SYS</t>
   </si>
   <si>
     <t>150065</t>
   </si>
   <si>
-    <t>Systolic left atrial pressure</t>
+    <t>MDC_PRESS_BLD_ATR_LEFT_SYS</t>
   </si>
   <si>
     <t>150067</t>
   </si>
   <si>
-    <t>Mean left atrial pressure</t>
+    <t>MDC_PRESS_BLD_ATR_LEFT_MEAN</t>
   </si>
   <si>
     <t>150071</t>
   </si>
   <si>
-    <t>Mean right atrial pressure</t>
+    <t>MDC_PRESS_BLD_ATR_RIGHT_MEAN</t>
   </si>
   <si>
     <t>150066</t>
   </si>
   <si>
-    <t>Diastolic left atrial pressure</t>
+    <t>MDC_PRESS_BLD_ATR_LEFT_DIA</t>
   </si>
   <si>
     <t>150070</t>
   </si>
   <si>
-    <t>Diastolic right atrial pressure</t>
+    <t>MDC_PRESS_BLD_ATR_RIGHT_DIA</t>
+  </si>
+  <si>
+    <t>153604</t>
+  </si>
+  <si>
+    <t>MDC_PRESS_CEREB_PERF</t>
   </si>
   <si>
     <t>188420</t>
   </si>
   <si>
-    <t>Rectal temperature</t>
+    <t>MDC_TEMP_RECT</t>
   </si>
   <si>
     <t>188496</t>
   </si>
   <si>
-    <t>Axillary temperature</t>
+    <t>MDC_TEMP_AXIL</t>
   </si>
   <si>
     <t>188424</t>
   </si>
   <si>
-    <t>Oral temperature</t>
+    <t>MDC_TEMP_ORAL</t>
   </si>
   <si>
     <t>188436</t>
   </si>
   <si>
-    <t>Blood temperature</t>
+    <t>MDC_TEMP_BLD</t>
   </si>
   <si>
     <t>188500</t>
   </si>
   <si>
-    <t>Myocardial temperature</t>
+    <t>MDC_TEMP_MYO</t>
   </si>
   <si>
     <t>147842</t>
   </si>
   <si>
-    <t>Heart Rate</t>
+    <t>MDC_ECG_HEART_RATE</t>
   </si>
   <si>
     <t>188504</t>
   </si>
   <si>
-    <t>Nasal temperature</t>
+    <t>MDC_TEMP_NASAL</t>
   </si>
   <si>
     <t>149514</t>
   </si>
   <si>
-    <t>Pulse rate</t>
+    <t>MDC_PULS_RATE</t>
   </si>
   <si>
     <t>150380</t>
   </si>
   <si>
-    <t>Nasopharynx temperature</t>
+    <t>MDC_TEMP_NASOPH</t>
   </si>
   <si>
     <t>188452</t>
   </si>
   <si>
-    <t>Axillary (armpit) temperature</t>
+    <t>MDC_TEMP_AXILLA</t>
   </si>
   <si>
     <t>150324</t>
   </si>
   <si>
+    <t>MDC_SAT_O2_ART</t>
+  </si>
+  <si>
     <t>150372</t>
   </si>
   <si>
+    <t>MDC_TEMP_ESOPH</t>
+  </si>
+  <si>
     <t>188796</t>
   </si>
   <si>
-    <t>Ideal body weight (IBW)</t>
+    <t>MDC_MASS_BODY_EST_IBW</t>
   </si>
   <si>
     <t>150392</t>
   </si>
   <si>
+    <t>MDC_TEMP_TYMP</t>
+  </si>
+  <si>
     <t>150356</t>
   </si>
   <si>
-    <t>Airway temperature</t>
+    <t>MDC_TEMP_AWAY</t>
   </si>
   <si>
     <t/>
@@ -639,7 +654,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B49"/>
+  <dimension ref="A1:B50"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -986,50 +1001,64 @@
       <c r="A43" t="s" s="2">
         <v>111</v>
       </c>
-      <c r="B43" s="2"/>
+      <c r="B43" t="s" s="2">
+        <v>112</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="B44" s="2"/>
+        <v>113</v>
+      </c>
+      <c r="B44" t="s" s="2">
+        <v>114</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>115</v>
-      </c>
-      <c r="B46" s="2"/>
+        <v>117</v>
+      </c>
+      <c r="B46" t="s" s="2">
+        <v>118</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>117</v>
+        <v>120</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>118</v>
+        <v>122</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>120</v>
+        <v>123</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="s" s="2">
+        <v>124</v>
+      </c>
+      <c r="B50" t="s" s="2">
+        <v>125</v>
       </c>
     </row>
   </sheetData>
